--- a/public/documents/requirement4/4_4/4_4_modelo_cadeia_de_valor.xlsx
+++ b/public/documents/requirement4/4_4/4_4_modelo_cadeia_de_valor.xlsx
@@ -1,28 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thiff\integra-sgi\integra-sgi\public\documents\requirement4\4_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F61B01AB-AA98-4A5B-B62F-ADEEDF20D013}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6B59F0F-26D2-480E-BBF6-E92841C0EC4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Cadeia de Valor" sheetId="1" r:id="rId1"/>
-    <sheet name="Guia Preenchimento" sheetId="2" r:id="rId2"/>
-    <sheet name="Folha2" sheetId="3" r:id="rId3"/>
+    <sheet name="Matriz de Processos" sheetId="4" r:id="rId1"/>
+    <sheet name="Guia Matriz" sheetId="5" r:id="rId2"/>
+    <sheet name="Cadeia de Valor" sheetId="1" r:id="rId3"/>
+    <sheet name="Guia Preenchimento" sheetId="2" r:id="rId4"/>
+    <sheet name="Esquema da Cadeia de Valor" sheetId="3" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="143">
   <si>
     <t>CADEIA DE VALOR</t>
   </si>
@@ -236,12 +238,277 @@
   <si>
     <t>-</t>
   </si>
+  <si>
+    <t>MATRIZ DE PROCESSOS INTEGRADOS</t>
+  </si>
+  <si>
+    <t>Nome do Processo</t>
+  </si>
+  <si>
+    <t>Tipo</t>
+  </si>
+  <si>
+    <t>Setor do Processo</t>
+  </si>
+  <si>
+    <t>Objetivo</t>
+  </si>
+  <si>
+    <t>Entradas</t>
+  </si>
+  <si>
+    <t>Saídas</t>
+  </si>
+  <si>
+    <t>Processos a Montante (ANTES)</t>
+  </si>
+  <si>
+    <t>Processos a Jusante (DEPOIS)</t>
+  </si>
+  <si>
+    <t>Recursos</t>
+  </si>
+  <si>
+    <t>Colaborador Responsável</t>
+  </si>
+  <si>
+    <t>Frequência de Processo</t>
+  </si>
+  <si>
+    <t>Riscos</t>
+  </si>
+  <si>
+    <t>Oportunidades</t>
+  </si>
+  <si>
+    <t>Compra da Materia Prima</t>
+  </si>
+  <si>
+    <t>Suporte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setor Financeiro </t>
+  </si>
+  <si>
+    <t>Garantir a aquisição da materia prima utilizada na nossa produção</t>
+  </si>
+  <si>
+    <t>Pedidos de compra espeficia</t>
+  </si>
+  <si>
+    <t>Encomendas emitidas; fornecedores avaliados</t>
+  </si>
+  <si>
+    <t>Receção da Materia Prima</t>
+  </si>
+  <si>
+    <t>Recursos Financeiros</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colaborado 01 </t>
+  </si>
+  <si>
+    <t>Mensal</t>
+  </si>
+  <si>
+    <t>Atraso na entrega por parte de fornecedores</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Negociar contratos-quadro com fornecedores de maneira estrategica </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Frequencia: Pode ser alterada exepcionalmente conforme demanda da produção </t>
+  </si>
+  <si>
+    <t>Compra de Embalagens</t>
+  </si>
+  <si>
+    <t>Garantir a aquisição de embalagens utilizada na nossa produção</t>
+  </si>
+  <si>
+    <t>Pedidos de compra especifico</t>
+  </si>
+  <si>
+    <t>Receção das Embalagens</t>
+  </si>
+  <si>
+    <t>Colaborado 02</t>
+  </si>
+  <si>
+    <t>Receção da Matéria-Prima</t>
+  </si>
+  <si>
+    <t>Operacional</t>
+  </si>
+  <si>
+    <t>Responsável de Produção</t>
+  </si>
+  <si>
+    <t>Garantir a receção e verificação de conformidade das carcaças e matérias-primas recebidas, incluindo verificação de temperatura, documentação veterinária e rastreabilidade</t>
+  </si>
+  <si>
+    <t>Carcaças/matérias-primas; guias de transporte; boletins veterinários; especificações de fornecedor</t>
+  </si>
+  <si>
+    <t>Matéria-prima aceite e registada; registos de receção e temperatura; NC de receção identificadas</t>
+  </si>
+  <si>
+    <t>Compras e Gestão de Fornecedores</t>
+  </si>
+  <si>
+    <t>Desmancha e Corte; Armazenamento Refrigerado e Congelado</t>
+  </si>
+  <si>
+    <t>Câmaras de receção; balança calibrada; termómetro; EPIs; sistema de registo</t>
+  </si>
+  <si>
+    <t>Responsável de Receção</t>
+  </si>
+  <si>
+    <t>Diária</t>
+  </si>
+  <si>
+    <t>Receção de matéria-prima fora da temperatura de segurança; documentação veterinária incompleta</t>
+  </si>
+  <si>
+    <t>Estabelecer especificações técnicas de receção com fornecedores homologados para reduzir rejeições</t>
+  </si>
+  <si>
+    <t>GUIA DE PRENCHIMENTO DA MATRIZ DE PROCESSOS</t>
+  </si>
+  <si>
+    <t>COMO PREENCHER A COLUNA "Tipo"</t>
+  </si>
+  <si>
+    <t>Coluna</t>
+  </si>
+  <si>
+    <t>Quando utilizar</t>
+  </si>
+  <si>
+    <t>Código</t>
+  </si>
+  <si>
+    <t>Identificador único do processo. Recomenda-se utilizar a sequência PR-01, PR-02, PR-03... para facilitar a organização e a rastreabilidade.</t>
+  </si>
+  <si>
+    <t>Processos diretamente ligados à atividade principal da empresa e que agregam valor ao produto ou serviço. Ex.: Produção, Receção da Matéria-Prima, Embalamento, Expedição.</t>
+  </si>
+  <si>
+    <t>Nome que descreve claramente a atividade realizada. Ex.: Compra da Matéria-Prima, Receção da Matéria-Prima, Gestão de Resíduos.</t>
+  </si>
+  <si>
+    <t>Processos que fornecem apoio aos processos operacionais. Ex.: Compras, Recursos Humanos, Manutenção, Tecnologia da Informação.</t>
+  </si>
+  <si>
+    <t>Classificação do processo conforme o mapa de processos do SGI. A seleção é feita através da lista suspensa (Validação de Dados) existente na planilha. Cada tipo possui uma cor correspondente para facilitar a identificação visual.</t>
+  </si>
+  <si>
+    <t>Gestão</t>
+  </si>
+  <si>
+    <t>Processos relacionados ao planeamento, direção, avaliação e melhoria do Sistema de Gestão. Ex.: Planeamento Estratégico, Auditorias, Revisão pela Gestão.</t>
+  </si>
+  <si>
+    <t>Área ou departamento responsável pela execução do processo. Ex.: Produção, Financeiro, Recursos Humanos, Qualidade, Ambiente, SST.</t>
+  </si>
+  <si>
+    <t>Ambiente</t>
+  </si>
+  <si>
+    <t>Processos voltados para o Sistema de Gestão Ambiental. Ex.: Gestão de Resíduos, Gestão de Efluentes, Monitorização Ambiental.</t>
+  </si>
+  <si>
+    <t>Descreve a finalidade do processo e o resultado esperado. Deve responder à pergunta: "Por que este processo existe?".</t>
+  </si>
+  <si>
+    <t>SST</t>
+  </si>
+  <si>
+    <t>Processos relacionados à Segurança e Saúde no Trabalho. Ex.: Gestão de EPI, Identificação de Perigos, Emergências, Vigilância da Saúde.</t>
+  </si>
+  <si>
+    <t>Recursos, documentos, informações ou materiais necessários para iniciar o processo.</t>
+  </si>
+  <si>
+    <t>Qualidade</t>
+  </si>
+  <si>
+    <t>Processos específicos da Gestão da Qualidade. Ex.: Controlo da Qualidade, Tratamento de Não Conformidades, Gestão de Reclamações, Satisfação do Cliente.</t>
+  </si>
+  <si>
+    <t>Produtos, documentos, informações ou resultados gerados após a execução do processo.</t>
+  </si>
+  <si>
+    <t>Melhoria</t>
+  </si>
+  <si>
+    <t>Processos destinados à melhoria contínua do Sistema de Gestão. Ex.: Ações Corretivas, Ações Preventivas, Melhoria Contínua, Lições Aprendidas.</t>
+  </si>
+  <si>
+    <t>Processos a Montante (Antecessores)</t>
+  </si>
+  <si>
+    <t>Processo que fornece a entrada necessária para que este processo possa iniciar. Caso seja o primeiro processo da cadeia, pode ser indicado "-" ou "Não aplicável".</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cambria"/>
+        <family val="1"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>Nota</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Cambria"/>
+        <family val="1"/>
+        <scheme val="major"/>
+      </rPr>
+      <t>: A classificação deve considerar a finalidade principal do processo. Em caso de dúvida, deve ser escolhida a categoria que melhor representa o seu papel dentro do Sistema de Gestão Integrado.</t>
+    </r>
+  </si>
+  <si>
+    <t>Processos a Jusante (Sucessores)</t>
+  </si>
+  <si>
+    <t>Processo que recebe a saída gerada por este processo.</t>
+  </si>
+  <si>
+    <t>Recursos humanos, equipamentos, infraestrutura, sistemas, ferramentas ou materiais utilizados durante a execução.</t>
+  </si>
+  <si>
+    <t>Função ou cargo responsável pelo processo. Sempre que possível, recomenda-se utilizar o cargo em vez do nome do colaborador, facilitando futuras alterações organizacionais.</t>
+  </si>
+  <si>
+    <t>Frequência do Processo</t>
+  </si>
+  <si>
+    <t>Periodicidade de execução. Ex.: Diária, Semanal, Mensal, Anual ou Conforme Necessidade.</t>
+  </si>
+  <si>
+    <t>Situações que podem comprometer o desempenho do processo ou impedir que seus objetivos sejam atingidos.</t>
+  </si>
+  <si>
+    <t>Melhorias que podem aumentar a eficiência, reduzir custos, minimizar riscos ou melhorar os resultados do processo.</t>
+  </si>
+  <si>
+    <t>Informações adicionais importantes, como exceções, particularidades, requisitos legais ou notas de utilização.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -363,8 +630,58 @@
       <family val="1"/>
       <scheme val="major"/>
     </font>
+    <font>
+      <b/>
+      <sz val="48"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Cambria"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Cambria"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Cambria"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Cambria"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="0"/>
+      <name val="Cambria"/>
+      <family val="1"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Cambria"/>
+      <family val="1"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <b/>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Cambria"/>
+      <family val="1"/>
+      <scheme val="major"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -394,8 +711,80 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF203E5E"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF0F7343"/>
+        <bgColor rgb="FF003366"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8DB4E2"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCD5B4"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF980206"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.499984740745262"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -483,85 +872,168 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="17" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -588,6 +1060,116 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>106680</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1029855</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>120042</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagem 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1814322C-2B5C-483C-A671-4AC588907C2B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="106680" y="0"/>
+          <a:ext cx="1037475" cy="1019202"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>60961</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1028701</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>127735</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagem 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{567E8611-03BE-4949-9384-A1DADF65CAFF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="129541" y="0"/>
+          <a:ext cx="967740" cy="950695"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -642,7 +1224,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -697,7 +1279,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1047,6 +1629,476 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19D9C300-2E8C-4E5C-B4C8-F232D6FDDBFC}">
+  <dimension ref="B1:O8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="1.6640625" customWidth="1"/>
+    <col min="2" max="2" width="23" customWidth="1"/>
+    <col min="3" max="3" width="17.44140625" customWidth="1"/>
+    <col min="4" max="4" width="18.44140625" customWidth="1"/>
+    <col min="5" max="5" width="26.88671875" customWidth="1"/>
+    <col min="6" max="6" width="18.88671875" customWidth="1"/>
+    <col min="7" max="7" width="18.5546875" customWidth="1"/>
+    <col min="8" max="8" width="30.6640625" customWidth="1"/>
+    <col min="9" max="9" width="20.109375" customWidth="1"/>
+    <col min="10" max="10" width="18.109375" customWidth="1"/>
+    <col min="11" max="11" width="18.44140625" customWidth="1"/>
+    <col min="12" max="12" width="29.109375" customWidth="1"/>
+    <col min="13" max="13" width="16.21875" customWidth="1"/>
+    <col min="14" max="14" width="25.109375" customWidth="1"/>
+    <col min="15" max="15" width="16.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:15" ht="4.2" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:15" ht="59.4" x14ac:dyDescent="0.3">
+      <c r="B2" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="30"/>
+      <c r="G2" s="30"/>
+      <c r="H2" s="30"/>
+      <c r="I2" s="30"/>
+      <c r="J2" s="30"/>
+      <c r="K2" s="30"/>
+      <c r="L2" s="30"/>
+      <c r="M2" s="30"/>
+      <c r="N2" s="30"/>
+      <c r="O2" s="30"/>
+    </row>
+    <row r="3" spans="2:15" ht="7.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="6"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="6"/>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
+    </row>
+    <row r="4" spans="2:15" x14ac:dyDescent="0.3">
+      <c r="B4" s="6"/>
+      <c r="C4" s="6"/>
+      <c r="D4" s="6"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="6"/>
+    </row>
+    <row r="5" spans="2:15" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="B5" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>66</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="J5" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="K5" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="M5" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="N5" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="O5" s="8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="6" spans="2:15" ht="66" x14ac:dyDescent="0.3">
+      <c r="B6" s="9" t="s">
+        <v>76</v>
+      </c>
+      <c r="C6" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="E6" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="F6" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="G6" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="H6" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="I6" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="J6" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="K6" s="11" t="s">
+        <v>84</v>
+      </c>
+      <c r="L6" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="M6" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="N6" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="O6" s="11" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="7" spans="2:15" ht="66" x14ac:dyDescent="0.3">
+      <c r="B7" s="9" t="s">
+        <v>89</v>
+      </c>
+      <c r="C7" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="D7" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="E7" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="F7" s="11" t="s">
+        <v>91</v>
+      </c>
+      <c r="G7" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="H7" s="11" t="s">
+        <v>61</v>
+      </c>
+      <c r="I7" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="J7" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="K7" s="11" t="s">
+        <v>93</v>
+      </c>
+      <c r="L7" s="11" t="s">
+        <v>85</v>
+      </c>
+      <c r="M7" s="11" t="s">
+        <v>86</v>
+      </c>
+      <c r="N7" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="O7" s="11" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="8" spans="2:15" ht="110.4" x14ac:dyDescent="0.3">
+      <c r="B8" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="E8" s="14" t="s">
+        <v>97</v>
+      </c>
+      <c r="F8" s="14" t="s">
+        <v>98</v>
+      </c>
+      <c r="G8" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="H8" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="I8" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="J8" s="14" t="s">
+        <v>102</v>
+      </c>
+      <c r="K8" s="14" t="s">
+        <v>103</v>
+      </c>
+      <c r="L8" s="15" t="s">
+        <v>104</v>
+      </c>
+      <c r="M8" s="14" t="s">
+        <v>105</v>
+      </c>
+      <c r="N8" s="11" t="s">
+        <v>106</v>
+      </c>
+      <c r="O8" s="15"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:O2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6D03841-9909-4FC3-8738-8C2F645B563D}">
+  <dimension ref="B1:F19"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="1" style="18" customWidth="1"/>
+    <col min="2" max="2" width="16.5546875" style="27" customWidth="1"/>
+    <col min="3" max="3" width="82.109375" style="18" customWidth="1"/>
+    <col min="4" max="4" width="1" style="18" customWidth="1"/>
+    <col min="5" max="5" width="17.77734375" style="18" customWidth="1"/>
+    <col min="6" max="6" width="73.88671875" style="18" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="8.88671875" style="18"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:6" ht="7.8" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:6" ht="57" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C2" s="26" t="s">
+        <v>107</v>
+      </c>
+      <c r="E2" s="28" t="s">
+        <v>108</v>
+      </c>
+      <c r="F2" s="28"/>
+    </row>
+    <row r="4" spans="2:6" ht="15" x14ac:dyDescent="0.3">
+      <c r="B4" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="C4" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="F4" s="16" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="5" spans="2:6" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="B5" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>95</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="B6" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E6" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="B7" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E7" s="21" t="s">
+        <v>117</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="B8" s="16" t="s">
+        <v>65</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>120</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="9" spans="2:6" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="B9" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E9" s="23" t="s">
+        <v>123</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="B10" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="E10" s="24" t="s">
+        <v>126</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="11" spans="2:6" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="B11" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E11" s="25" t="s">
+        <v>129</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="12" spans="2:6" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="B12" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="E12" s="29" t="s">
+        <v>133</v>
+      </c>
+      <c r="F12" s="29"/>
+    </row>
+    <row r="13" spans="2:6" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="B13" s="16" t="s">
+        <v>134</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="14" spans="2:6" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="B14" s="16" t="s">
+        <v>71</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="B15" s="16" t="s">
+        <v>72</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="B16" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="17" spans="2:3" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="B17" s="16" t="s">
+        <v>74</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="18" spans="2:3" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="B18" s="16" t="s">
+        <v>75</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="19" spans="2:3" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="B19" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>142</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="E12:F12"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -1073,1051 +2125,1064 @@
   <sheetData>
     <row r="1" spans="2:62" ht="11.4" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:62" ht="61.2" customHeight="1" x14ac:dyDescent="0.55000000000000004">
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="52" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="8"/>
-      <c r="D2" s="8"/>
-      <c r="E2" s="8"/>
-      <c r="F2" s="8"/>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
-      <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
-      <c r="K2" s="8"/>
-      <c r="L2" s="8"/>
-      <c r="M2" s="8"/>
-      <c r="N2" s="8"/>
-      <c r="O2" s="8"/>
-      <c r="P2" s="8"/>
-      <c r="Q2" s="8"/>
-      <c r="R2" s="8"/>
-      <c r="S2" s="8"/>
-      <c r="T2" s="8"/>
-      <c r="U2" s="8"/>
-      <c r="V2" s="8"/>
-      <c r="W2" s="8"/>
-      <c r="X2" s="8"/>
-      <c r="Y2" s="8"/>
-      <c r="Z2" s="8"/>
-      <c r="AA2" s="8"/>
-      <c r="AB2" s="8"/>
-      <c r="AC2" s="8"/>
-      <c r="AD2" s="8"/>
-      <c r="AE2" s="8"/>
-      <c r="AF2" s="8"/>
-      <c r="AG2" s="8"/>
-      <c r="AH2" s="8"/>
-      <c r="AI2" s="8"/>
-      <c r="AJ2" s="8"/>
-      <c r="AK2" s="8"/>
-      <c r="AL2" s="8"/>
-      <c r="AM2" s="8"/>
-      <c r="AN2" s="8"/>
-      <c r="AO2" s="8"/>
-      <c r="AP2" s="8"/>
-      <c r="AQ2" s="8"/>
-      <c r="AR2" s="8"/>
-      <c r="AS2" s="8"/>
-      <c r="AT2" s="8"/>
-      <c r="AU2" s="8"/>
-      <c r="AV2" s="8"/>
-      <c r="AW2" s="8"/>
-      <c r="AX2" s="8"/>
-      <c r="AY2" s="8"/>
-      <c r="AZ2" s="8"/>
-      <c r="BA2" s="8"/>
-      <c r="BB2" s="8"/>
-      <c r="BC2" s="8"/>
-      <c r="BD2" s="8"/>
-      <c r="BE2" s="8"/>
-      <c r="BF2" s="8"/>
-      <c r="BG2" s="8"/>
-      <c r="BH2" s="8"/>
-      <c r="BI2" s="8"/>
-      <c r="BJ2" s="8"/>
+      <c r="C2" s="53"/>
+      <c r="D2" s="53"/>
+      <c r="E2" s="53"/>
+      <c r="F2" s="53"/>
+      <c r="G2" s="53"/>
+      <c r="H2" s="53"/>
+      <c r="I2" s="53"/>
+      <c r="J2" s="53"/>
+      <c r="K2" s="53"/>
+      <c r="L2" s="53"/>
+      <c r="M2" s="53"/>
+      <c r="N2" s="53"/>
+      <c r="O2" s="53"/>
+      <c r="P2" s="53"/>
+      <c r="Q2" s="53"/>
+      <c r="R2" s="53"/>
+      <c r="S2" s="53"/>
+      <c r="T2" s="53"/>
+      <c r="U2" s="53"/>
+      <c r="V2" s="53"/>
+      <c r="W2" s="53"/>
+      <c r="X2" s="53"/>
+      <c r="Y2" s="53"/>
+      <c r="Z2" s="53"/>
+      <c r="AA2" s="53"/>
+      <c r="AB2" s="53"/>
+      <c r="AC2" s="53"/>
+      <c r="AD2" s="53"/>
+      <c r="AE2" s="53"/>
+      <c r="AF2" s="53"/>
+      <c r="AG2" s="53"/>
+      <c r="AH2" s="53"/>
+      <c r="AI2" s="53"/>
+      <c r="AJ2" s="53"/>
+      <c r="AK2" s="53"/>
+      <c r="AL2" s="53"/>
+      <c r="AM2" s="53"/>
+      <c r="AN2" s="53"/>
+      <c r="AO2" s="53"/>
+      <c r="AP2" s="53"/>
+      <c r="AQ2" s="53"/>
+      <c r="AR2" s="53"/>
+      <c r="AS2" s="53"/>
+      <c r="AT2" s="53"/>
+      <c r="AU2" s="53"/>
+      <c r="AV2" s="53"/>
+      <c r="AW2" s="53"/>
+      <c r="AX2" s="53"/>
+      <c r="AY2" s="53"/>
+      <c r="AZ2" s="53"/>
+      <c r="BA2" s="53"/>
+      <c r="BB2" s="53"/>
+      <c r="BC2" s="53"/>
+      <c r="BD2" s="53"/>
+      <c r="BE2" s="53"/>
+      <c r="BF2" s="53"/>
+      <c r="BG2" s="53"/>
+      <c r="BH2" s="53"/>
+      <c r="BI2" s="53"/>
+      <c r="BJ2" s="53"/>
     </row>
     <row r="3" spans="2:62" ht="15.6" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="4" spans="2:62" ht="37.200000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="31" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="11"/>
-      <c r="L4" s="11"/>
-      <c r="M4" s="11"/>
-      <c r="N4" s="11"/>
-      <c r="O4" s="11"/>
-      <c r="P4" s="11"/>
-      <c r="Q4" s="11"/>
-      <c r="R4" s="11"/>
-      <c r="S4" s="11"/>
-      <c r="T4" s="11"/>
-      <c r="U4" s="11"/>
-      <c r="V4" s="11"/>
-      <c r="W4" s="11"/>
-      <c r="X4" s="11"/>
-      <c r="Y4" s="11"/>
-      <c r="Z4" s="11"/>
-      <c r="AA4" s="11"/>
-      <c r="AB4" s="11"/>
-      <c r="AC4" s="11"/>
-      <c r="AD4" s="11"/>
-      <c r="AE4" s="11"/>
-      <c r="AF4" s="11"/>
-      <c r="AG4" s="11"/>
-      <c r="AH4" s="11"/>
-      <c r="AI4" s="11"/>
-      <c r="AJ4" s="11"/>
-      <c r="AK4" s="11"/>
-      <c r="AL4" s="11"/>
-      <c r="AM4" s="11"/>
-      <c r="AN4" s="11"/>
-      <c r="AO4" s="11"/>
-      <c r="AP4" s="11"/>
-      <c r="AQ4" s="11"/>
-      <c r="AR4" s="11"/>
-      <c r="AS4" s="11"/>
-      <c r="AT4" s="11"/>
-      <c r="AU4" s="11"/>
-      <c r="AV4" s="11"/>
-      <c r="AW4" s="11"/>
-      <c r="AX4" s="11"/>
-      <c r="AY4" s="11"/>
-      <c r="AZ4" s="11"/>
-      <c r="BA4" s="11"/>
-      <c r="BB4" s="11"/>
-      <c r="BC4" s="11"/>
-      <c r="BD4" s="11"/>
-      <c r="BE4" s="11"/>
-      <c r="BF4" s="11"/>
-      <c r="BG4" s="11"/>
-      <c r="BH4" s="11"/>
-      <c r="BI4" s="11"/>
-      <c r="BJ4" s="11"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
+      <c r="F4" s="32"/>
+      <c r="G4" s="32"/>
+      <c r="H4" s="32"/>
+      <c r="I4" s="32"/>
+      <c r="J4" s="32"/>
+      <c r="K4" s="32"/>
+      <c r="L4" s="32"/>
+      <c r="M4" s="32"/>
+      <c r="N4" s="32"/>
+      <c r="O4" s="32"/>
+      <c r="P4" s="32"/>
+      <c r="Q4" s="32"/>
+      <c r="R4" s="32"/>
+      <c r="S4" s="32"/>
+      <c r="T4" s="32"/>
+      <c r="U4" s="32"/>
+      <c r="V4" s="32"/>
+      <c r="W4" s="32"/>
+      <c r="X4" s="32"/>
+      <c r="Y4" s="32"/>
+      <c r="Z4" s="32"/>
+      <c r="AA4" s="32"/>
+      <c r="AB4" s="32"/>
+      <c r="AC4" s="32"/>
+      <c r="AD4" s="32"/>
+      <c r="AE4" s="32"/>
+      <c r="AF4" s="32"/>
+      <c r="AG4" s="32"/>
+      <c r="AH4" s="32"/>
+      <c r="AI4" s="32"/>
+      <c r="AJ4" s="32"/>
+      <c r="AK4" s="32"/>
+      <c r="AL4" s="32"/>
+      <c r="AM4" s="32"/>
+      <c r="AN4" s="32"/>
+      <c r="AO4" s="32"/>
+      <c r="AP4" s="32"/>
+      <c r="AQ4" s="32"/>
+      <c r="AR4" s="32"/>
+      <c r="AS4" s="32"/>
+      <c r="AT4" s="32"/>
+      <c r="AU4" s="32"/>
+      <c r="AV4" s="32"/>
+      <c r="AW4" s="32"/>
+      <c r="AX4" s="32"/>
+      <c r="AY4" s="32"/>
+      <c r="AZ4" s="32"/>
+      <c r="BA4" s="32"/>
+      <c r="BB4" s="32"/>
+      <c r="BC4" s="32"/>
+      <c r="BD4" s="32"/>
+      <c r="BE4" s="32"/>
+      <c r="BF4" s="32"/>
+      <c r="BG4" s="32"/>
+      <c r="BH4" s="32"/>
+      <c r="BI4" s="32"/>
+      <c r="BJ4" s="32"/>
     </row>
     <row r="5" spans="2:62" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="6"/>
-      <c r="AE5" s="18" t="s">
+      <c r="B5" s="51"/>
+      <c r="AE5" s="55" t="s">
         <v>3</v>
       </c>
-      <c r="AF5" s="2"/>
-      <c r="AG5" s="2"/>
-      <c r="AH5" s="2"/>
+      <c r="AF5" s="34"/>
+      <c r="AG5" s="34"/>
+      <c r="AH5" s="34"/>
     </row>
     <row r="6" spans="2:62" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="6"/>
-      <c r="C6" s="12" t="s">
+      <c r="B6" s="51"/>
+      <c r="C6" s="37" t="s">
         <v>4</v>
       </c>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="13"/>
-      <c r="K6" s="13"/>
-      <c r="L6" s="13"/>
-      <c r="M6" s="13"/>
-      <c r="N6" s="13"/>
-      <c r="O6" s="13"/>
-      <c r="P6" s="13"/>
-      <c r="Q6" s="13"/>
-      <c r="R6" s="13"/>
-      <c r="S6" s="13"/>
-      <c r="T6" s="13"/>
-      <c r="U6" s="13"/>
-      <c r="V6" s="13"/>
-      <c r="W6" s="13"/>
-      <c r="X6" s="13"/>
-      <c r="Y6" s="13"/>
-      <c r="Z6" s="13"/>
-      <c r="AA6" s="13"/>
-      <c r="AB6" s="13"/>
-      <c r="AC6" s="13"/>
-      <c r="AD6" s="13"/>
-      <c r="AE6" s="13"/>
-      <c r="AF6" s="13"/>
-      <c r="AG6" s="13"/>
-      <c r="AH6" s="13"/>
-      <c r="AI6" s="13"/>
-      <c r="AJ6" s="13"/>
-      <c r="AK6" s="13"/>
-      <c r="AL6" s="13"/>
-      <c r="AM6" s="13"/>
-      <c r="AN6" s="13"/>
-      <c r="AO6" s="13"/>
-      <c r="AP6" s="13"/>
-      <c r="AQ6" s="13"/>
-      <c r="AR6" s="13"/>
-      <c r="AS6" s="13"/>
-      <c r="AT6" s="13"/>
-      <c r="AU6" s="13"/>
-      <c r="AV6" s="13"/>
-      <c r="AW6" s="13"/>
-      <c r="AX6" s="13"/>
-      <c r="AY6" s="13"/>
-      <c r="AZ6" s="13"/>
-      <c r="BA6" s="13"/>
-      <c r="BB6" s="13"/>
-      <c r="BC6" s="13"/>
-      <c r="BD6" s="13"/>
-      <c r="BE6" s="13"/>
-      <c r="BF6" s="13"/>
-      <c r="BG6" s="13"/>
-      <c r="BH6" s="13"/>
-      <c r="BI6" s="13"/>
-      <c r="BJ6" s="13"/>
+      <c r="D6" s="38"/>
+      <c r="E6" s="38"/>
+      <c r="F6" s="38"/>
+      <c r="G6" s="38"/>
+      <c r="H6" s="38"/>
+      <c r="I6" s="38"/>
+      <c r="J6" s="38"/>
+      <c r="K6" s="38"/>
+      <c r="L6" s="38"/>
+      <c r="M6" s="38"/>
+      <c r="N6" s="38"/>
+      <c r="O6" s="38"/>
+      <c r="P6" s="38"/>
+      <c r="Q6" s="38"/>
+      <c r="R6" s="38"/>
+      <c r="S6" s="38"/>
+      <c r="T6" s="38"/>
+      <c r="U6" s="38"/>
+      <c r="V6" s="38"/>
+      <c r="W6" s="38"/>
+      <c r="X6" s="38"/>
+      <c r="Y6" s="38"/>
+      <c r="Z6" s="38"/>
+      <c r="AA6" s="38"/>
+      <c r="AB6" s="38"/>
+      <c r="AC6" s="38"/>
+      <c r="AD6" s="38"/>
+      <c r="AE6" s="38"/>
+      <c r="AF6" s="38"/>
+      <c r="AG6" s="38"/>
+      <c r="AH6" s="38"/>
+      <c r="AI6" s="38"/>
+      <c r="AJ6" s="38"/>
+      <c r="AK6" s="38"/>
+      <c r="AL6" s="38"/>
+      <c r="AM6" s="38"/>
+      <c r="AN6" s="38"/>
+      <c r="AO6" s="38"/>
+      <c r="AP6" s="38"/>
+      <c r="AQ6" s="38"/>
+      <c r="AR6" s="38"/>
+      <c r="AS6" s="38"/>
+      <c r="AT6" s="38"/>
+      <c r="AU6" s="38"/>
+      <c r="AV6" s="38"/>
+      <c r="AW6" s="38"/>
+      <c r="AX6" s="38"/>
+      <c r="AY6" s="38"/>
+      <c r="AZ6" s="38"/>
+      <c r="BA6" s="38"/>
+      <c r="BB6" s="38"/>
+      <c r="BC6" s="38"/>
+      <c r="BD6" s="38"/>
+      <c r="BE6" s="38"/>
+      <c r="BF6" s="38"/>
+      <c r="BG6" s="38"/>
+      <c r="BH6" s="38"/>
+      <c r="BI6" s="38"/>
+      <c r="BJ6" s="38"/>
     </row>
     <row r="7" spans="2:62" ht="41.4" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="6"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4"/>
-      <c r="K7" s="4"/>
-      <c r="L7" s="4"/>
-      <c r="M7" s="3"/>
-      <c r="N7" s="4"/>
-      <c r="O7" s="4"/>
-      <c r="P7" s="4"/>
-      <c r="Q7" s="4"/>
-      <c r="R7" s="4"/>
-      <c r="S7" s="4"/>
-      <c r="T7" s="4"/>
-      <c r="U7" s="4"/>
-      <c r="V7" s="4"/>
-      <c r="W7" s="3"/>
-      <c r="X7" s="4"/>
-      <c r="Y7" s="4"/>
-      <c r="Z7" s="4"/>
-      <c r="AA7" s="4"/>
-      <c r="AB7" s="4"/>
-      <c r="AC7" s="4"/>
-      <c r="AD7" s="4"/>
-      <c r="AE7" s="4"/>
-      <c r="AF7" s="4"/>
-      <c r="AG7" s="3"/>
-      <c r="AH7" s="4"/>
-      <c r="AI7" s="4"/>
-      <c r="AJ7" s="4"/>
-      <c r="AK7" s="4"/>
-      <c r="AL7" s="4"/>
-      <c r="AM7" s="4"/>
-      <c r="AN7" s="4"/>
-      <c r="AO7" s="4"/>
-      <c r="AP7" s="4"/>
-      <c r="AQ7" s="3"/>
-      <c r="AR7" s="4"/>
-      <c r="AS7" s="4"/>
-      <c r="AT7" s="4"/>
-      <c r="AU7" s="4"/>
-      <c r="AV7" s="4"/>
-      <c r="AW7" s="4"/>
-      <c r="AX7" s="4"/>
-      <c r="AY7" s="4"/>
-      <c r="AZ7" s="4"/>
-      <c r="BA7" s="3"/>
-      <c r="BB7" s="4"/>
-      <c r="BC7" s="4"/>
-      <c r="BD7" s="4"/>
-      <c r="BE7" s="4"/>
-      <c r="BF7" s="4"/>
-      <c r="BG7" s="4"/>
-      <c r="BH7" s="4"/>
-      <c r="BI7" s="4"/>
-      <c r="BJ7" s="4"/>
+      <c r="B7" s="51"/>
+      <c r="C7" s="42"/>
+      <c r="D7" s="36"/>
+      <c r="E7" s="36"/>
+      <c r="F7" s="36"/>
+      <c r="G7" s="36"/>
+      <c r="H7" s="36"/>
+      <c r="I7" s="36"/>
+      <c r="J7" s="36"/>
+      <c r="K7" s="36"/>
+      <c r="L7" s="36"/>
+      <c r="M7" s="35"/>
+      <c r="N7" s="36"/>
+      <c r="O7" s="36"/>
+      <c r="P7" s="36"/>
+      <c r="Q7" s="36"/>
+      <c r="R7" s="36"/>
+      <c r="S7" s="36"/>
+      <c r="T7" s="36"/>
+      <c r="U7" s="36"/>
+      <c r="V7" s="36"/>
+      <c r="W7" s="35"/>
+      <c r="X7" s="36"/>
+      <c r="Y7" s="36"/>
+      <c r="Z7" s="36"/>
+      <c r="AA7" s="36"/>
+      <c r="AB7" s="36"/>
+      <c r="AC7" s="36"/>
+      <c r="AD7" s="36"/>
+      <c r="AE7" s="36"/>
+      <c r="AF7" s="36"/>
+      <c r="AG7" s="35"/>
+      <c r="AH7" s="36"/>
+      <c r="AI7" s="36"/>
+      <c r="AJ7" s="36"/>
+      <c r="AK7" s="36"/>
+      <c r="AL7" s="36"/>
+      <c r="AM7" s="36"/>
+      <c r="AN7" s="36"/>
+      <c r="AO7" s="36"/>
+      <c r="AP7" s="36"/>
+      <c r="AQ7" s="35"/>
+      <c r="AR7" s="36"/>
+      <c r="AS7" s="36"/>
+      <c r="AT7" s="36"/>
+      <c r="AU7" s="36"/>
+      <c r="AV7" s="36"/>
+      <c r="AW7" s="36"/>
+      <c r="AX7" s="36"/>
+      <c r="AY7" s="36"/>
+      <c r="AZ7" s="36"/>
+      <c r="BA7" s="35"/>
+      <c r="BB7" s="36"/>
+      <c r="BC7" s="36"/>
+      <c r="BD7" s="36"/>
+      <c r="BE7" s="36"/>
+      <c r="BF7" s="36"/>
+      <c r="BG7" s="36"/>
+      <c r="BH7" s="36"/>
+      <c r="BI7" s="36"/>
+      <c r="BJ7" s="36"/>
     </row>
     <row r="8" spans="2:62" ht="7.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="6"/>
+      <c r="B8" s="51"/>
     </row>
     <row r="9" spans="2:62" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="6"/>
-      <c r="C9" s="12" t="s">
+      <c r="B9" s="51"/>
+      <c r="C9" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13"/>
-      <c r="H9" s="13"/>
-      <c r="I9" s="13"/>
-      <c r="J9" s="13"/>
-      <c r="K9" s="13"/>
-      <c r="L9" s="13"/>
-      <c r="M9" s="13"/>
-      <c r="N9" s="13"/>
-      <c r="O9" s="13"/>
-      <c r="P9" s="13"/>
-      <c r="Q9" s="13"/>
-      <c r="R9" s="13"/>
-      <c r="S9" s="13"/>
-      <c r="T9" s="13"/>
-      <c r="U9" s="13"/>
-      <c r="V9" s="13"/>
-      <c r="W9" s="13"/>
-      <c r="X9" s="13"/>
-      <c r="Y9" s="13"/>
-      <c r="Z9" s="13"/>
-      <c r="AA9" s="13"/>
-      <c r="AB9" s="13"/>
-      <c r="AC9" s="13"/>
-      <c r="AD9" s="13"/>
-      <c r="AE9" s="13"/>
-      <c r="AF9" s="13"/>
-      <c r="AG9" s="13"/>
-      <c r="AH9" s="13"/>
-      <c r="AI9" s="13"/>
-      <c r="AJ9" s="13"/>
-      <c r="AK9" s="13"/>
-      <c r="AL9" s="13"/>
-      <c r="AM9" s="13"/>
-      <c r="AN9" s="13"/>
-      <c r="AO9" s="13"/>
-      <c r="AP9" s="13"/>
-      <c r="AQ9" s="13"/>
-      <c r="AR9" s="13"/>
-      <c r="AS9" s="13"/>
-      <c r="AT9" s="13"/>
-      <c r="AU9" s="13"/>
-      <c r="AV9" s="13"/>
-      <c r="AW9" s="13"/>
-      <c r="AX9" s="13"/>
-      <c r="AY9" s="13"/>
-      <c r="AZ9" s="13"/>
-      <c r="BA9" s="13"/>
-      <c r="BB9" s="13"/>
-      <c r="BC9" s="13"/>
-      <c r="BD9" s="13"/>
-      <c r="BE9" s="13"/>
-      <c r="BF9" s="13"/>
-      <c r="BG9" s="13"/>
-      <c r="BH9" s="13"/>
-      <c r="BI9" s="13"/>
-      <c r="BJ9" s="13"/>
+      <c r="D9" s="38"/>
+      <c r="E9" s="38"/>
+      <c r="F9" s="38"/>
+      <c r="G9" s="38"/>
+      <c r="H9" s="38"/>
+      <c r="I9" s="38"/>
+      <c r="J9" s="38"/>
+      <c r="K9" s="38"/>
+      <c r="L9" s="38"/>
+      <c r="M9" s="38"/>
+      <c r="N9" s="38"/>
+      <c r="O9" s="38"/>
+      <c r="P9" s="38"/>
+      <c r="Q9" s="38"/>
+      <c r="R9" s="38"/>
+      <c r="S9" s="38"/>
+      <c r="T9" s="38"/>
+      <c r="U9" s="38"/>
+      <c r="V9" s="38"/>
+      <c r="W9" s="38"/>
+      <c r="X9" s="38"/>
+      <c r="Y9" s="38"/>
+      <c r="Z9" s="38"/>
+      <c r="AA9" s="38"/>
+      <c r="AB9" s="38"/>
+      <c r="AC9" s="38"/>
+      <c r="AD9" s="38"/>
+      <c r="AE9" s="38"/>
+      <c r="AF9" s="38"/>
+      <c r="AG9" s="38"/>
+      <c r="AH9" s="38"/>
+      <c r="AI9" s="38"/>
+      <c r="AJ9" s="38"/>
+      <c r="AK9" s="38"/>
+      <c r="AL9" s="38"/>
+      <c r="AM9" s="38"/>
+      <c r="AN9" s="38"/>
+      <c r="AO9" s="38"/>
+      <c r="AP9" s="38"/>
+      <c r="AQ9" s="38"/>
+      <c r="AR9" s="38"/>
+      <c r="AS9" s="38"/>
+      <c r="AT9" s="38"/>
+      <c r="AU9" s="38"/>
+      <c r="AV9" s="38"/>
+      <c r="AW9" s="38"/>
+      <c r="AX9" s="38"/>
+      <c r="AY9" s="38"/>
+      <c r="AZ9" s="38"/>
+      <c r="BA9" s="38"/>
+      <c r="BB9" s="38"/>
+      <c r="BC9" s="38"/>
+      <c r="BD9" s="38"/>
+      <c r="BE9" s="38"/>
+      <c r="BF9" s="38"/>
+      <c r="BG9" s="38"/>
+      <c r="BH9" s="38"/>
+      <c r="BI9" s="38"/>
+      <c r="BJ9" s="38"/>
     </row>
     <row r="10" spans="2:62" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="6"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="4"/>
-      <c r="J10" s="4"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="4"/>
-      <c r="M10" s="4"/>
-      <c r="N10" s="4"/>
-      <c r="O10" s="4"/>
-      <c r="P10" s="4"/>
-      <c r="Q10" s="4"/>
-      <c r="R10" s="4"/>
-      <c r="S10" s="3"/>
-      <c r="T10" s="4"/>
-      <c r="U10" s="4"/>
-      <c r="V10" s="4"/>
-      <c r="W10" s="4"/>
-      <c r="X10" s="4"/>
-      <c r="Y10" s="4"/>
-      <c r="Z10" s="4"/>
-      <c r="AA10" s="3"/>
-      <c r="AB10" s="4"/>
-      <c r="AC10" s="4"/>
-      <c r="AD10" s="4"/>
-      <c r="AE10" s="4"/>
-      <c r="AF10" s="4"/>
-      <c r="AG10" s="4"/>
-      <c r="AH10" s="4"/>
-      <c r="AI10" s="3"/>
-      <c r="AJ10" s="4"/>
-      <c r="AK10" s="4"/>
-      <c r="AL10" s="4"/>
-      <c r="AM10" s="4"/>
-      <c r="AN10" s="4"/>
-      <c r="AO10" s="4"/>
-      <c r="AP10" s="3"/>
-      <c r="AQ10" s="4"/>
-      <c r="AR10" s="4"/>
-      <c r="AS10" s="4"/>
-      <c r="AT10" s="4"/>
-      <c r="AU10" s="4"/>
-      <c r="AV10" s="4"/>
-      <c r="AW10" s="3"/>
-      <c r="AX10" s="4"/>
-      <c r="AY10" s="4"/>
-      <c r="AZ10" s="4"/>
-      <c r="BA10" s="4"/>
-      <c r="BB10" s="4"/>
-      <c r="BC10" s="4"/>
-      <c r="BD10" s="3"/>
-      <c r="BE10" s="4"/>
-      <c r="BF10" s="4"/>
-      <c r="BG10" s="4"/>
-      <c r="BH10" s="4"/>
-      <c r="BI10" s="4"/>
-      <c r="BJ10" s="4"/>
+      <c r="B10" s="51"/>
+      <c r="C10" s="42"/>
+      <c r="D10" s="36"/>
+      <c r="E10" s="36"/>
+      <c r="F10" s="36"/>
+      <c r="G10" s="36"/>
+      <c r="H10" s="36"/>
+      <c r="I10" s="36"/>
+      <c r="J10" s="36"/>
+      <c r="K10" s="35"/>
+      <c r="L10" s="36"/>
+      <c r="M10" s="36"/>
+      <c r="N10" s="36"/>
+      <c r="O10" s="36"/>
+      <c r="P10" s="36"/>
+      <c r="Q10" s="36"/>
+      <c r="R10" s="36"/>
+      <c r="S10" s="35"/>
+      <c r="T10" s="36"/>
+      <c r="U10" s="36"/>
+      <c r="V10" s="36"/>
+      <c r="W10" s="36"/>
+      <c r="X10" s="36"/>
+      <c r="Y10" s="36"/>
+      <c r="Z10" s="36"/>
+      <c r="AA10" s="35"/>
+      <c r="AB10" s="36"/>
+      <c r="AC10" s="36"/>
+      <c r="AD10" s="36"/>
+      <c r="AE10" s="36"/>
+      <c r="AF10" s="36"/>
+      <c r="AG10" s="36"/>
+      <c r="AH10" s="36"/>
+      <c r="AI10" s="35"/>
+      <c r="AJ10" s="36"/>
+      <c r="AK10" s="36"/>
+      <c r="AL10" s="36"/>
+      <c r="AM10" s="36"/>
+      <c r="AN10" s="36"/>
+      <c r="AO10" s="36"/>
+      <c r="AP10" s="35"/>
+      <c r="AQ10" s="36"/>
+      <c r="AR10" s="36"/>
+      <c r="AS10" s="36"/>
+      <c r="AT10" s="36"/>
+      <c r="AU10" s="36"/>
+      <c r="AV10" s="36"/>
+      <c r="AW10" s="35"/>
+      <c r="AX10" s="36"/>
+      <c r="AY10" s="36"/>
+      <c r="AZ10" s="36"/>
+      <c r="BA10" s="36"/>
+      <c r="BB10" s="36"/>
+      <c r="BC10" s="36"/>
+      <c r="BD10" s="35"/>
+      <c r="BE10" s="36"/>
+      <c r="BF10" s="36"/>
+      <c r="BG10" s="36"/>
+      <c r="BH10" s="36"/>
+      <c r="BI10" s="36"/>
+      <c r="BJ10" s="36"/>
     </row>
     <row r="11" spans="2:62" ht="7.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="6"/>
+      <c r="B11" s="51"/>
     </row>
     <row r="12" spans="2:62" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="6"/>
-      <c r="C12" s="12" t="s">
+      <c r="B12" s="51"/>
+      <c r="C12" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="13"/>
-      <c r="H12" s="13"/>
-      <c r="I12" s="13"/>
-      <c r="J12" s="13"/>
-      <c r="K12" s="13"/>
-      <c r="L12" s="13"/>
-      <c r="M12" s="13"/>
-      <c r="N12" s="13"/>
-      <c r="O12" s="13"/>
-      <c r="P12" s="13"/>
-      <c r="Q12" s="13"/>
-      <c r="R12" s="13"/>
-      <c r="S12" s="13"/>
-      <c r="T12" s="13"/>
-      <c r="U12" s="13"/>
-      <c r="V12" s="13"/>
-      <c r="W12" s="13"/>
-      <c r="X12" s="13"/>
-      <c r="Y12" s="13"/>
-      <c r="Z12" s="13"/>
-      <c r="AA12" s="13"/>
-      <c r="AB12" s="13"/>
-      <c r="AC12" s="13"/>
-      <c r="AD12" s="13"/>
-      <c r="AE12" s="13"/>
-      <c r="AF12" s="13"/>
-      <c r="AG12" s="13"/>
-      <c r="AH12" s="13"/>
-      <c r="AI12" s="13"/>
-      <c r="AJ12" s="13"/>
-      <c r="AK12" s="13"/>
-      <c r="AL12" s="13"/>
-      <c r="AM12" s="13"/>
-      <c r="AN12" s="13"/>
-      <c r="AO12" s="13"/>
-      <c r="AP12" s="13"/>
-      <c r="AQ12" s="13"/>
-      <c r="AR12" s="13"/>
-      <c r="AS12" s="13"/>
-      <c r="AT12" s="13"/>
-      <c r="AU12" s="13"/>
-      <c r="AV12" s="13"/>
-      <c r="AW12" s="13"/>
-      <c r="AX12" s="13"/>
-      <c r="AY12" s="13"/>
-      <c r="AZ12" s="13"/>
-      <c r="BA12" s="13"/>
-      <c r="BB12" s="13"/>
-      <c r="BC12" s="13"/>
-      <c r="BD12" s="13"/>
-      <c r="BE12" s="13"/>
-      <c r="BF12" s="13"/>
-      <c r="BG12" s="13"/>
-      <c r="BH12" s="13"/>
-      <c r="BI12" s="13"/>
-      <c r="BJ12" s="13"/>
+      <c r="D12" s="38"/>
+      <c r="E12" s="38"/>
+      <c r="F12" s="38"/>
+      <c r="G12" s="38"/>
+      <c r="H12" s="38"/>
+      <c r="I12" s="38"/>
+      <c r="J12" s="38"/>
+      <c r="K12" s="38"/>
+      <c r="L12" s="38"/>
+      <c r="M12" s="38"/>
+      <c r="N12" s="38"/>
+      <c r="O12" s="38"/>
+      <c r="P12" s="38"/>
+      <c r="Q12" s="38"/>
+      <c r="R12" s="38"/>
+      <c r="S12" s="38"/>
+      <c r="T12" s="38"/>
+      <c r="U12" s="38"/>
+      <c r="V12" s="38"/>
+      <c r="W12" s="38"/>
+      <c r="X12" s="38"/>
+      <c r="Y12" s="38"/>
+      <c r="Z12" s="38"/>
+      <c r="AA12" s="38"/>
+      <c r="AB12" s="38"/>
+      <c r="AC12" s="38"/>
+      <c r="AD12" s="38"/>
+      <c r="AE12" s="38"/>
+      <c r="AF12" s="38"/>
+      <c r="AG12" s="38"/>
+      <c r="AH12" s="38"/>
+      <c r="AI12" s="38"/>
+      <c r="AJ12" s="38"/>
+      <c r="AK12" s="38"/>
+      <c r="AL12" s="38"/>
+      <c r="AM12" s="38"/>
+      <c r="AN12" s="38"/>
+      <c r="AO12" s="38"/>
+      <c r="AP12" s="38"/>
+      <c r="AQ12" s="38"/>
+      <c r="AR12" s="38"/>
+      <c r="AS12" s="38"/>
+      <c r="AT12" s="38"/>
+      <c r="AU12" s="38"/>
+      <c r="AV12" s="38"/>
+      <c r="AW12" s="38"/>
+      <c r="AX12" s="38"/>
+      <c r="AY12" s="38"/>
+      <c r="AZ12" s="38"/>
+      <c r="BA12" s="38"/>
+      <c r="BB12" s="38"/>
+      <c r="BC12" s="38"/>
+      <c r="BD12" s="38"/>
+      <c r="BE12" s="38"/>
+      <c r="BF12" s="38"/>
+      <c r="BG12" s="38"/>
+      <c r="BH12" s="38"/>
+      <c r="BI12" s="38"/>
+      <c r="BJ12" s="38"/>
     </row>
     <row r="13" spans="2:62" ht="37.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="6"/>
-      <c r="C13" s="23" t="s">
+      <c r="B13" s="51"/>
+      <c r="C13" s="48" t="s">
         <v>7</v>
       </c>
-      <c r="D13" s="22"/>
-      <c r="E13" s="22"/>
-      <c r="F13" s="22"/>
-      <c r="G13" s="22"/>
-      <c r="H13" s="22"/>
-      <c r="I13" s="22"/>
-      <c r="J13" s="22"/>
-      <c r="K13" s="19" t="s">
+      <c r="D13" s="44"/>
+      <c r="E13" s="44"/>
+      <c r="F13" s="44"/>
+      <c r="G13" s="44"/>
+      <c r="H13" s="44"/>
+      <c r="I13" s="44"/>
+      <c r="J13" s="44"/>
+      <c r="K13" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="L13" s="2"/>
-      <c r="M13" s="20"/>
-      <c r="N13" s="4"/>
-      <c r="O13" s="4"/>
-      <c r="P13" s="4"/>
-      <c r="Q13" s="4"/>
-      <c r="R13" s="19" t="s">
+      <c r="L13" s="34"/>
+      <c r="M13" s="39"/>
+      <c r="N13" s="36"/>
+      <c r="O13" s="36"/>
+      <c r="P13" s="36"/>
+      <c r="Q13" s="36"/>
+      <c r="R13" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="S13" s="2"/>
-      <c r="T13" s="20"/>
-      <c r="U13" s="4"/>
-      <c r="V13" s="4"/>
-      <c r="W13" s="4"/>
-      <c r="X13" s="4"/>
-      <c r="Y13" s="19" t="s">
+      <c r="S13" s="34"/>
+      <c r="T13" s="39"/>
+      <c r="U13" s="36"/>
+      <c r="V13" s="36"/>
+      <c r="W13" s="36"/>
+      <c r="X13" s="36"/>
+      <c r="Y13" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="Z13" s="2"/>
-      <c r="AA13" s="20"/>
-      <c r="AB13" s="4"/>
-      <c r="AC13" s="4"/>
-      <c r="AD13" s="4"/>
-      <c r="AE13" s="4"/>
-      <c r="AF13" s="19" t="s">
+      <c r="Z13" s="34"/>
+      <c r="AA13" s="39"/>
+      <c r="AB13" s="36"/>
+      <c r="AC13" s="36"/>
+      <c r="AD13" s="36"/>
+      <c r="AE13" s="36"/>
+      <c r="AF13" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="AG13" s="2"/>
-      <c r="AH13" s="20"/>
-      <c r="AI13" s="4"/>
-      <c r="AJ13" s="4"/>
-      <c r="AK13" s="4"/>
-      <c r="AL13" s="4"/>
-      <c r="AM13" s="19" t="s">
+      <c r="AG13" s="34"/>
+      <c r="AH13" s="39"/>
+      <c r="AI13" s="36"/>
+      <c r="AJ13" s="36"/>
+      <c r="AK13" s="36"/>
+      <c r="AL13" s="36"/>
+      <c r="AM13" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="AN13" s="2"/>
-      <c r="AO13" s="20"/>
-      <c r="AP13" s="4"/>
-      <c r="AQ13" s="4"/>
-      <c r="AR13" s="4"/>
-      <c r="AS13" s="4"/>
-      <c r="AT13" s="19" t="s">
+      <c r="AN13" s="34"/>
+      <c r="AO13" s="39"/>
+      <c r="AP13" s="36"/>
+      <c r="AQ13" s="36"/>
+      <c r="AR13" s="36"/>
+      <c r="AS13" s="36"/>
+      <c r="AT13" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="AU13" s="2"/>
-      <c r="AV13" s="20"/>
-      <c r="AW13" s="4"/>
-      <c r="AX13" s="4"/>
-      <c r="AY13" s="4"/>
-      <c r="AZ13" s="4"/>
-      <c r="BA13" s="19" t="s">
+      <c r="AU13" s="34"/>
+      <c r="AV13" s="39"/>
+      <c r="AW13" s="36"/>
+      <c r="AX13" s="36"/>
+      <c r="AY13" s="36"/>
+      <c r="AZ13" s="36"/>
+      <c r="BA13" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="BB13" s="2"/>
-      <c r="BC13" s="21" t="s">
+      <c r="BB13" s="34"/>
+      <c r="BC13" s="43" t="s">
         <v>9</v>
       </c>
-      <c r="BD13" s="22"/>
-      <c r="BE13" s="22"/>
-      <c r="BF13" s="22"/>
-      <c r="BG13" s="22"/>
-      <c r="BH13" s="22"/>
-      <c r="BI13" s="22"/>
-      <c r="BJ13" s="22"/>
+      <c r="BD13" s="44"/>
+      <c r="BE13" s="44"/>
+      <c r="BF13" s="44"/>
+      <c r="BG13" s="44"/>
+      <c r="BH13" s="44"/>
+      <c r="BI13" s="44"/>
+      <c r="BJ13" s="44"/>
     </row>
     <row r="14" spans="2:62" ht="7.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="6"/>
+      <c r="B14" s="51"/>
     </row>
     <row r="15" spans="2:62" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="6"/>
-      <c r="C15" s="12" t="s">
+      <c r="B15" s="51"/>
+      <c r="C15" s="37" t="s">
         <v>10</v>
       </c>
-      <c r="D15" s="13"/>
-      <c r="E15" s="13"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="13"/>
-      <c r="H15" s="13"/>
-      <c r="I15" s="13"/>
-      <c r="J15" s="13"/>
-      <c r="K15" s="13"/>
-      <c r="L15" s="13"/>
-      <c r="M15" s="13"/>
-      <c r="N15" s="13"/>
-      <c r="O15" s="13"/>
-      <c r="P15" s="13"/>
-      <c r="Q15" s="13"/>
-      <c r="R15" s="13"/>
-      <c r="S15" s="13"/>
-      <c r="T15" s="13"/>
-      <c r="U15" s="13"/>
-      <c r="V15" s="13"/>
-      <c r="W15" s="13"/>
-      <c r="X15" s="13"/>
-      <c r="Y15" s="13"/>
-      <c r="Z15" s="13"/>
-      <c r="AA15" s="13"/>
-      <c r="AB15" s="13"/>
-      <c r="AC15" s="13"/>
-      <c r="AD15" s="13"/>
-      <c r="AE15" s="13"/>
-      <c r="AF15" s="13"/>
-      <c r="AG15" s="13"/>
-      <c r="AH15" s="13"/>
-      <c r="AI15" s="13"/>
-      <c r="AJ15" s="13"/>
-      <c r="AK15" s="13"/>
-      <c r="AL15" s="13"/>
-      <c r="AM15" s="13"/>
-      <c r="AN15" s="13"/>
-      <c r="AO15" s="13"/>
-      <c r="AP15" s="13"/>
-      <c r="AQ15" s="13"/>
-      <c r="AR15" s="13"/>
-      <c r="AS15" s="13"/>
-      <c r="AT15" s="13"/>
-      <c r="AU15" s="13"/>
-      <c r="AV15" s="13"/>
-      <c r="AW15" s="13"/>
-      <c r="AX15" s="13"/>
-      <c r="AY15" s="13"/>
-      <c r="AZ15" s="13"/>
-      <c r="BA15" s="13"/>
-      <c r="BB15" s="13"/>
-      <c r="BC15" s="13"/>
-      <c r="BD15" s="13"/>
-      <c r="BE15" s="13"/>
-      <c r="BF15" s="13"/>
-      <c r="BG15" s="13"/>
-      <c r="BH15" s="13"/>
-      <c r="BI15" s="13"/>
-      <c r="BJ15" s="13"/>
+      <c r="D15" s="38"/>
+      <c r="E15" s="38"/>
+      <c r="F15" s="38"/>
+      <c r="G15" s="38"/>
+      <c r="H15" s="38"/>
+      <c r="I15" s="38"/>
+      <c r="J15" s="38"/>
+      <c r="K15" s="38"/>
+      <c r="L15" s="38"/>
+      <c r="M15" s="38"/>
+      <c r="N15" s="38"/>
+      <c r="O15" s="38"/>
+      <c r="P15" s="38"/>
+      <c r="Q15" s="38"/>
+      <c r="R15" s="38"/>
+      <c r="S15" s="38"/>
+      <c r="T15" s="38"/>
+      <c r="U15" s="38"/>
+      <c r="V15" s="38"/>
+      <c r="W15" s="38"/>
+      <c r="X15" s="38"/>
+      <c r="Y15" s="38"/>
+      <c r="Z15" s="38"/>
+      <c r="AA15" s="38"/>
+      <c r="AB15" s="38"/>
+      <c r="AC15" s="38"/>
+      <c r="AD15" s="38"/>
+      <c r="AE15" s="38"/>
+      <c r="AF15" s="38"/>
+      <c r="AG15" s="38"/>
+      <c r="AH15" s="38"/>
+      <c r="AI15" s="38"/>
+      <c r="AJ15" s="38"/>
+      <c r="AK15" s="38"/>
+      <c r="AL15" s="38"/>
+      <c r="AM15" s="38"/>
+      <c r="AN15" s="38"/>
+      <c r="AO15" s="38"/>
+      <c r="AP15" s="38"/>
+      <c r="AQ15" s="38"/>
+      <c r="AR15" s="38"/>
+      <c r="AS15" s="38"/>
+      <c r="AT15" s="38"/>
+      <c r="AU15" s="38"/>
+      <c r="AV15" s="38"/>
+      <c r="AW15" s="38"/>
+      <c r="AX15" s="38"/>
+      <c r="AY15" s="38"/>
+      <c r="AZ15" s="38"/>
+      <c r="BA15" s="38"/>
+      <c r="BB15" s="38"/>
+      <c r="BC15" s="38"/>
+      <c r="BD15" s="38"/>
+      <c r="BE15" s="38"/>
+      <c r="BF15" s="38"/>
+      <c r="BG15" s="38"/>
+      <c r="BH15" s="38"/>
+      <c r="BI15" s="38"/>
+      <c r="BJ15" s="38"/>
     </row>
     <row r="16" spans="2:62" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="6"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4"/>
-      <c r="H16" s="4"/>
-      <c r="I16" s="4"/>
-      <c r="J16" s="4"/>
-      <c r="K16" s="3"/>
-      <c r="L16" s="4"/>
-      <c r="M16" s="4"/>
-      <c r="N16" s="4"/>
-      <c r="O16" s="4"/>
-      <c r="P16" s="4"/>
-      <c r="Q16" s="4"/>
-      <c r="R16" s="4"/>
-      <c r="S16" s="3"/>
-      <c r="T16" s="4"/>
-      <c r="U16" s="4"/>
-      <c r="V16" s="4"/>
-      <c r="W16" s="4"/>
-      <c r="X16" s="4"/>
-      <c r="Y16" s="4"/>
-      <c r="Z16" s="4"/>
-      <c r="AA16" s="3"/>
-      <c r="AB16" s="4"/>
-      <c r="AC16" s="4"/>
-      <c r="AD16" s="4"/>
-      <c r="AE16" s="4"/>
-      <c r="AF16" s="4"/>
-      <c r="AG16" s="4"/>
-      <c r="AH16" s="4"/>
-      <c r="AI16" s="3"/>
-      <c r="AJ16" s="4"/>
-      <c r="AK16" s="4"/>
-      <c r="AL16" s="4"/>
-      <c r="AM16" s="4"/>
-      <c r="AN16" s="4"/>
-      <c r="AO16" s="4"/>
-      <c r="AP16" s="3"/>
-      <c r="AQ16" s="4"/>
-      <c r="AR16" s="4"/>
-      <c r="AS16" s="4"/>
-      <c r="AT16" s="4"/>
-      <c r="AU16" s="4"/>
-      <c r="AV16" s="4"/>
-      <c r="AW16" s="3"/>
-      <c r="AX16" s="4"/>
-      <c r="AY16" s="4"/>
-      <c r="AZ16" s="4"/>
-      <c r="BA16" s="4"/>
-      <c r="BB16" s="4"/>
-      <c r="BC16" s="4"/>
-      <c r="BD16" s="3"/>
-      <c r="BE16" s="4"/>
-      <c r="BF16" s="4"/>
-      <c r="BG16" s="4"/>
-      <c r="BH16" s="4"/>
-      <c r="BI16" s="4"/>
-      <c r="BJ16" s="4"/>
+      <c r="B16" s="51"/>
+      <c r="C16" s="42"/>
+      <c r="D16" s="36"/>
+      <c r="E16" s="36"/>
+      <c r="F16" s="36"/>
+      <c r="G16" s="36"/>
+      <c r="H16" s="36"/>
+      <c r="I16" s="36"/>
+      <c r="J16" s="36"/>
+      <c r="K16" s="35"/>
+      <c r="L16" s="36"/>
+      <c r="M16" s="36"/>
+      <c r="N16" s="36"/>
+      <c r="O16" s="36"/>
+      <c r="P16" s="36"/>
+      <c r="Q16" s="36"/>
+      <c r="R16" s="36"/>
+      <c r="S16" s="35"/>
+      <c r="T16" s="36"/>
+      <c r="U16" s="36"/>
+      <c r="V16" s="36"/>
+      <c r="W16" s="36"/>
+      <c r="X16" s="36"/>
+      <c r="Y16" s="36"/>
+      <c r="Z16" s="36"/>
+      <c r="AA16" s="35"/>
+      <c r="AB16" s="36"/>
+      <c r="AC16" s="36"/>
+      <c r="AD16" s="36"/>
+      <c r="AE16" s="36"/>
+      <c r="AF16" s="36"/>
+      <c r="AG16" s="36"/>
+      <c r="AH16" s="36"/>
+      <c r="AI16" s="35"/>
+      <c r="AJ16" s="36"/>
+      <c r="AK16" s="36"/>
+      <c r="AL16" s="36"/>
+      <c r="AM16" s="36"/>
+      <c r="AN16" s="36"/>
+      <c r="AO16" s="36"/>
+      <c r="AP16" s="35"/>
+      <c r="AQ16" s="36"/>
+      <c r="AR16" s="36"/>
+      <c r="AS16" s="36"/>
+      <c r="AT16" s="36"/>
+      <c r="AU16" s="36"/>
+      <c r="AV16" s="36"/>
+      <c r="AW16" s="35"/>
+      <c r="AX16" s="36"/>
+      <c r="AY16" s="36"/>
+      <c r="AZ16" s="36"/>
+      <c r="BA16" s="36"/>
+      <c r="BB16" s="36"/>
+      <c r="BC16" s="36"/>
+      <c r="BD16" s="35"/>
+      <c r="BE16" s="36"/>
+      <c r="BF16" s="36"/>
+      <c r="BG16" s="36"/>
+      <c r="BH16" s="36"/>
+      <c r="BI16" s="36"/>
+      <c r="BJ16" s="36"/>
     </row>
     <row r="17" spans="2:63" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="6"/>
-      <c r="AE17" s="18" t="s">
+      <c r="B17" s="51"/>
+      <c r="AE17" s="55" t="s">
         <v>3</v>
       </c>
-      <c r="AF17" s="2"/>
-      <c r="AG17" s="2"/>
-      <c r="AH17" s="2"/>
+      <c r="AF17" s="34"/>
+      <c r="AG17" s="34"/>
+      <c r="AH17" s="34"/>
     </row>
     <row r="18" spans="2:63" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="6"/>
-      <c r="C18" s="16" t="s">
+      <c r="B18" s="51"/>
+      <c r="C18" s="49" t="s">
         <v>11</v>
       </c>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="17"/>
-      <c r="G18" s="17"/>
-      <c r="H18" s="17"/>
-      <c r="I18" s="17"/>
-      <c r="J18" s="17"/>
-      <c r="K18" s="17"/>
-      <c r="L18" s="17"/>
-      <c r="M18" s="17"/>
-      <c r="N18" s="17"/>
-      <c r="O18" s="17"/>
-      <c r="P18" s="17"/>
-      <c r="Q18" s="17"/>
-      <c r="R18" s="17"/>
-      <c r="S18" s="17"/>
-      <c r="T18" s="17"/>
-      <c r="U18" s="17"/>
-      <c r="V18" s="17"/>
-      <c r="W18" s="17"/>
-      <c r="X18" s="17"/>
-      <c r="Y18" s="17"/>
-      <c r="Z18" s="17"/>
-      <c r="AA18" s="17"/>
-      <c r="AB18" s="17"/>
-      <c r="AC18" s="17"/>
-      <c r="AD18" s="17"/>
-      <c r="AE18" s="17"/>
-      <c r="AF18" s="17"/>
-      <c r="AG18" s="17"/>
-      <c r="AH18" s="17"/>
-      <c r="AI18" s="17"/>
-      <c r="AJ18" s="17"/>
-      <c r="AK18" s="17"/>
-      <c r="AL18" s="17"/>
-      <c r="AM18" s="17"/>
-      <c r="AN18" s="17"/>
-      <c r="AO18" s="17"/>
-      <c r="AP18" s="17"/>
-      <c r="AQ18" s="17"/>
-      <c r="AR18" s="17"/>
-      <c r="AS18" s="17"/>
-      <c r="AT18" s="17"/>
-      <c r="AU18" s="17"/>
-      <c r="AV18" s="17"/>
-      <c r="AW18" s="17"/>
-      <c r="AX18" s="17"/>
-      <c r="AY18" s="17"/>
-      <c r="AZ18" s="17"/>
-      <c r="BA18" s="17"/>
-      <c r="BB18" s="17"/>
-      <c r="BC18" s="17"/>
-      <c r="BD18" s="17"/>
-      <c r="BE18" s="17"/>
-      <c r="BF18" s="17"/>
-      <c r="BG18" s="17"/>
-      <c r="BH18" s="17"/>
-      <c r="BI18" s="17"/>
-      <c r="BJ18" s="17"/>
+      <c r="D18" s="32"/>
+      <c r="E18" s="32"/>
+      <c r="F18" s="32"/>
+      <c r="G18" s="32"/>
+      <c r="H18" s="32"/>
+      <c r="I18" s="32"/>
+      <c r="J18" s="32"/>
+      <c r="K18" s="32"/>
+      <c r="L18" s="32"/>
+      <c r="M18" s="32"/>
+      <c r="N18" s="32"/>
+      <c r="O18" s="32"/>
+      <c r="P18" s="32"/>
+      <c r="Q18" s="32"/>
+      <c r="R18" s="32"/>
+      <c r="S18" s="32"/>
+      <c r="T18" s="32"/>
+      <c r="U18" s="32"/>
+      <c r="V18" s="32"/>
+      <c r="W18" s="32"/>
+      <c r="X18" s="32"/>
+      <c r="Y18" s="32"/>
+      <c r="Z18" s="32"/>
+      <c r="AA18" s="32"/>
+      <c r="AB18" s="32"/>
+      <c r="AC18" s="32"/>
+      <c r="AD18" s="32"/>
+      <c r="AE18" s="32"/>
+      <c r="AF18" s="32"/>
+      <c r="AG18" s="32"/>
+      <c r="AH18" s="32"/>
+      <c r="AI18" s="32"/>
+      <c r="AJ18" s="32"/>
+      <c r="AK18" s="32"/>
+      <c r="AL18" s="32"/>
+      <c r="AM18" s="32"/>
+      <c r="AN18" s="32"/>
+      <c r="AO18" s="32"/>
+      <c r="AP18" s="32"/>
+      <c r="AQ18" s="32"/>
+      <c r="AR18" s="32"/>
+      <c r="AS18" s="32"/>
+      <c r="AT18" s="32"/>
+      <c r="AU18" s="32"/>
+      <c r="AV18" s="32"/>
+      <c r="AW18" s="32"/>
+      <c r="AX18" s="32"/>
+      <c r="AY18" s="32"/>
+      <c r="AZ18" s="32"/>
+      <c r="BA18" s="32"/>
+      <c r="BB18" s="32"/>
+      <c r="BC18" s="32"/>
+      <c r="BD18" s="32"/>
+      <c r="BE18" s="32"/>
+      <c r="BF18" s="32"/>
+      <c r="BG18" s="32"/>
+      <c r="BH18" s="32"/>
+      <c r="BI18" s="32"/>
+      <c r="BJ18" s="32"/>
     </row>
     <row r="19" spans="2:63" ht="10.050000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="6"/>
+      <c r="B19" s="51"/>
     </row>
     <row r="20" spans="2:63" ht="16.05" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="6"/>
-      <c r="C20" s="14" t="s">
+      <c r="B20" s="51"/>
+      <c r="C20" s="40" t="s">
         <v>12</v>
       </c>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="15"/>
-      <c r="H20" s="15"/>
-      <c r="I20" s="15"/>
-      <c r="J20" s="15"/>
-      <c r="K20" s="15"/>
-      <c r="L20" s="15"/>
-      <c r="M20" s="15"/>
-      <c r="N20" s="15"/>
-      <c r="O20" s="15"/>
-      <c r="P20" s="15"/>
-      <c r="Q20" s="15"/>
-      <c r="R20" s="15"/>
-      <c r="S20" s="15"/>
-      <c r="T20" s="15"/>
-      <c r="U20" s="15"/>
-      <c r="V20" s="15"/>
-      <c r="W20" s="15"/>
-      <c r="X20" s="15"/>
-      <c r="Y20" s="15"/>
-      <c r="Z20" s="15"/>
-      <c r="AA20" s="15"/>
-      <c r="AB20" s="15"/>
-      <c r="AC20" s="15"/>
-      <c r="AD20" s="15"/>
-      <c r="AE20" s="15"/>
-      <c r="AF20" s="15"/>
-      <c r="AG20" s="15"/>
-      <c r="AH20" s="15"/>
-      <c r="AI20" s="15"/>
-      <c r="AJ20" s="15"/>
-      <c r="AK20" s="15"/>
-      <c r="AL20" s="15"/>
-      <c r="AM20" s="15"/>
-      <c r="AN20" s="15"/>
-      <c r="AO20" s="15"/>
-      <c r="AP20" s="15"/>
-      <c r="AQ20" s="15"/>
-      <c r="AR20" s="15"/>
-      <c r="AS20" s="15"/>
-      <c r="AT20" s="15"/>
-      <c r="AU20" s="15"/>
-      <c r="AV20" s="15"/>
-      <c r="AW20" s="15"/>
-      <c r="AX20" s="15"/>
-      <c r="AY20" s="15"/>
-      <c r="AZ20" s="15"/>
-      <c r="BA20" s="15"/>
-      <c r="BB20" s="15"/>
-      <c r="BC20" s="15"/>
-      <c r="BD20" s="15"/>
-      <c r="BE20" s="15"/>
-      <c r="BF20" s="15"/>
-      <c r="BG20" s="15"/>
-      <c r="BH20" s="15"/>
-      <c r="BI20" s="15"/>
-      <c r="BJ20" s="15"/>
+      <c r="D20" s="41"/>
+      <c r="E20" s="41"/>
+      <c r="F20" s="41"/>
+      <c r="G20" s="41"/>
+      <c r="H20" s="41"/>
+      <c r="I20" s="41"/>
+      <c r="J20" s="41"/>
+      <c r="K20" s="41"/>
+      <c r="L20" s="41"/>
+      <c r="M20" s="41"/>
+      <c r="N20" s="41"/>
+      <c r="O20" s="41"/>
+      <c r="P20" s="41"/>
+      <c r="Q20" s="41"/>
+      <c r="R20" s="41"/>
+      <c r="S20" s="41"/>
+      <c r="T20" s="41"/>
+      <c r="U20" s="41"/>
+      <c r="V20" s="41"/>
+      <c r="W20" s="41"/>
+      <c r="X20" s="41"/>
+      <c r="Y20" s="41"/>
+      <c r="Z20" s="41"/>
+      <c r="AA20" s="41"/>
+      <c r="AB20" s="41"/>
+      <c r="AC20" s="41"/>
+      <c r="AD20" s="41"/>
+      <c r="AE20" s="41"/>
+      <c r="AF20" s="41"/>
+      <c r="AG20" s="41"/>
+      <c r="AH20" s="41"/>
+      <c r="AI20" s="41"/>
+      <c r="AJ20" s="41"/>
+      <c r="AK20" s="41"/>
+      <c r="AL20" s="41"/>
+      <c r="AM20" s="41"/>
+      <c r="AN20" s="41"/>
+      <c r="AO20" s="41"/>
+      <c r="AP20" s="41"/>
+      <c r="AQ20" s="41"/>
+      <c r="AR20" s="41"/>
+      <c r="AS20" s="41"/>
+      <c r="AT20" s="41"/>
+      <c r="AU20" s="41"/>
+      <c r="AV20" s="41"/>
+      <c r="AW20" s="41"/>
+      <c r="AX20" s="41"/>
+      <c r="AY20" s="41"/>
+      <c r="AZ20" s="41"/>
+      <c r="BA20" s="41"/>
+      <c r="BB20" s="41"/>
+      <c r="BC20" s="41"/>
+      <c r="BD20" s="41"/>
+      <c r="BE20" s="41"/>
+      <c r="BF20" s="41"/>
+      <c r="BG20" s="41"/>
+      <c r="BH20" s="41"/>
+      <c r="BI20" s="41"/>
+      <c r="BJ20" s="41"/>
     </row>
     <row r="21" spans="2:63" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="6"/>
-      <c r="C21" s="24" t="s">
+      <c r="B21" s="51"/>
+      <c r="C21" s="54" t="s">
         <v>13</v>
       </c>
-      <c r="D21" s="25"/>
-      <c r="E21" s="25"/>
-      <c r="F21" s="25"/>
-      <c r="G21" s="25"/>
-      <c r="H21" s="25"/>
-      <c r="I21" s="25"/>
-      <c r="J21" s="25"/>
-      <c r="K21" s="25"/>
-      <c r="L21" s="25"/>
-      <c r="M21" s="25"/>
-      <c r="N21" s="25"/>
-      <c r="O21" s="19" t="s">
+      <c r="D21" s="47"/>
+      <c r="E21" s="47"/>
+      <c r="F21" s="47"/>
+      <c r="G21" s="47"/>
+      <c r="H21" s="47"/>
+      <c r="I21" s="47"/>
+      <c r="J21" s="47"/>
+      <c r="K21" s="47"/>
+      <c r="L21" s="47"/>
+      <c r="M21" s="47"/>
+      <c r="N21" s="47"/>
+      <c r="O21" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="P21" s="2"/>
-      <c r="Q21" s="2"/>
-      <c r="R21" s="26" t="s">
+      <c r="P21" s="34"/>
+      <c r="Q21" s="34"/>
+      <c r="R21" s="46" t="s">
         <v>14</v>
       </c>
-      <c r="S21" s="25"/>
-      <c r="T21" s="25"/>
-      <c r="U21" s="25"/>
-      <c r="V21" s="25"/>
-      <c r="W21" s="25"/>
-      <c r="X21" s="25"/>
-      <c r="Y21" s="25"/>
-      <c r="Z21" s="25"/>
-      <c r="AA21" s="25"/>
-      <c r="AB21" s="25"/>
-      <c r="AC21" s="25"/>
-      <c r="AD21" s="19" t="s">
+      <c r="S21" s="47"/>
+      <c r="T21" s="47"/>
+      <c r="U21" s="47"/>
+      <c r="V21" s="47"/>
+      <c r="W21" s="47"/>
+      <c r="X21" s="47"/>
+      <c r="Y21" s="47"/>
+      <c r="Z21" s="47"/>
+      <c r="AA21" s="47"/>
+      <c r="AB21" s="47"/>
+      <c r="AC21" s="47"/>
+      <c r="AD21" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="AE21" s="2"/>
-      <c r="AF21" s="2"/>
-      <c r="AG21" s="26" t="s">
+      <c r="AE21" s="34"/>
+      <c r="AF21" s="34"/>
+      <c r="AG21" s="46" t="s">
         <v>15</v>
       </c>
-      <c r="AH21" s="25"/>
-      <c r="AI21" s="25"/>
-      <c r="AJ21" s="25"/>
-      <c r="AK21" s="25"/>
-      <c r="AL21" s="25"/>
-      <c r="AM21" s="25"/>
-      <c r="AN21" s="25"/>
-      <c r="AO21" s="25"/>
-      <c r="AP21" s="25"/>
-      <c r="AQ21" s="25"/>
-      <c r="AR21" s="25"/>
-      <c r="AS21" s="19" t="s">
+      <c r="AH21" s="47"/>
+      <c r="AI21" s="47"/>
+      <c r="AJ21" s="47"/>
+      <c r="AK21" s="47"/>
+      <c r="AL21" s="47"/>
+      <c r="AM21" s="47"/>
+      <c r="AN21" s="47"/>
+      <c r="AO21" s="47"/>
+      <c r="AP21" s="47"/>
+      <c r="AQ21" s="47"/>
+      <c r="AR21" s="47"/>
+      <c r="AS21" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="AT21" s="2"/>
-      <c r="AU21" s="2"/>
-      <c r="AV21" s="26" t="s">
+      <c r="AT21" s="34"/>
+      <c r="AU21" s="34"/>
+      <c r="AV21" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="AW21" s="25"/>
-      <c r="AX21" s="25"/>
-      <c r="AY21" s="25"/>
-      <c r="AZ21" s="25"/>
-      <c r="BA21" s="25"/>
-      <c r="BB21" s="25"/>
-      <c r="BC21" s="25"/>
-      <c r="BD21" s="25"/>
-      <c r="BE21" s="25"/>
-      <c r="BF21" s="25"/>
-      <c r="BG21" s="25"/>
-      <c r="BH21" s="19" t="s">
+      <c r="AW21" s="47"/>
+      <c r="AX21" s="47"/>
+      <c r="AY21" s="47"/>
+      <c r="AZ21" s="47"/>
+      <c r="BA21" s="47"/>
+      <c r="BB21" s="47"/>
+      <c r="BC21" s="47"/>
+      <c r="BD21" s="47"/>
+      <c r="BE21" s="47"/>
+      <c r="BF21" s="47"/>
+      <c r="BG21" s="47"/>
+      <c r="BH21" s="33" t="s">
         <v>17</v>
       </c>
-      <c r="BI21" s="2"/>
-      <c r="BJ21" s="2"/>
+      <c r="BI21" s="34"/>
+      <c r="BJ21" s="34"/>
     </row>
     <row r="22" spans="2:63" ht="10.050000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="23" spans="2:63" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="30" t="s">
+      <c r="B23" s="45" t="s">
         <v>60</v>
       </c>
-      <c r="C23" s="30"/>
-      <c r="D23" s="30"/>
-      <c r="E23" s="30"/>
-      <c r="F23" s="30"/>
-      <c r="G23" s="30"/>
-      <c r="H23" s="30"/>
-      <c r="I23" s="30"/>
-      <c r="J23" s="30"/>
-      <c r="K23" s="30"/>
-      <c r="L23" s="30"/>
-      <c r="M23" s="30"/>
-      <c r="N23" s="30"/>
-      <c r="O23" s="30"/>
-      <c r="P23" s="30"/>
-      <c r="Q23" s="30"/>
-      <c r="R23" s="30"/>
-      <c r="S23" s="30"/>
-      <c r="T23" s="30"/>
-      <c r="U23" s="30"/>
-      <c r="V23" s="30"/>
-      <c r="W23" s="30"/>
-      <c r="X23" s="30"/>
-      <c r="Y23" s="30"/>
-      <c r="Z23" s="30"/>
-      <c r="AA23" s="30"/>
-      <c r="AB23" s="30"/>
-      <c r="AC23" s="30"/>
-      <c r="AD23" s="30"/>
-      <c r="AE23" s="30"/>
-      <c r="AF23" s="30"/>
-      <c r="AG23" s="30"/>
-      <c r="AH23" s="30"/>
-      <c r="AI23" s="30"/>
-      <c r="AJ23" s="30"/>
-      <c r="AK23" s="30"/>
-      <c r="AL23" s="30"/>
-      <c r="AM23" s="30"/>
-      <c r="AN23" s="30"/>
-      <c r="AO23" s="30"/>
-      <c r="AP23" s="30"/>
-      <c r="AQ23" s="30"/>
-      <c r="AR23" s="30"/>
-      <c r="AS23" s="30"/>
-      <c r="AT23" s="30"/>
-      <c r="AU23" s="30"/>
-      <c r="AV23" s="30"/>
-      <c r="AW23" s="30"/>
-      <c r="AX23" s="30"/>
-      <c r="AY23" s="30"/>
-      <c r="AZ23" s="30"/>
-      <c r="BA23" s="30"/>
-      <c r="BB23" s="30"/>
-      <c r="BC23" s="30"/>
-      <c r="BD23" s="30"/>
-      <c r="BE23" s="30"/>
-      <c r="BF23" s="30"/>
-      <c r="BG23" s="30"/>
-      <c r="BH23" s="30"/>
-      <c r="BI23" s="30"/>
-      <c r="BJ23" s="30"/>
-      <c r="BK23" s="30"/>
+      <c r="C23" s="45"/>
+      <c r="D23" s="45"/>
+      <c r="E23" s="45"/>
+      <c r="F23" s="45"/>
+      <c r="G23" s="45"/>
+      <c r="H23" s="45"/>
+      <c r="I23" s="45"/>
+      <c r="J23" s="45"/>
+      <c r="K23" s="45"/>
+      <c r="L23" s="45"/>
+      <c r="M23" s="45"/>
+      <c r="N23" s="45"/>
+      <c r="O23" s="45"/>
+      <c r="P23" s="45"/>
+      <c r="Q23" s="45"/>
+      <c r="R23" s="45"/>
+      <c r="S23" s="45"/>
+      <c r="T23" s="45"/>
+      <c r="U23" s="45"/>
+      <c r="V23" s="45"/>
+      <c r="W23" s="45"/>
+      <c r="X23" s="45"/>
+      <c r="Y23" s="45"/>
+      <c r="Z23" s="45"/>
+      <c r="AA23" s="45"/>
+      <c r="AB23" s="45"/>
+      <c r="AC23" s="45"/>
+      <c r="AD23" s="45"/>
+      <c r="AE23" s="45"/>
+      <c r="AF23" s="45"/>
+      <c r="AG23" s="45"/>
+      <c r="AH23" s="45"/>
+      <c r="AI23" s="45"/>
+      <c r="AJ23" s="45"/>
+      <c r="AK23" s="45"/>
+      <c r="AL23" s="45"/>
+      <c r="AM23" s="45"/>
+      <c r="AN23" s="45"/>
+      <c r="AO23" s="45"/>
+      <c r="AP23" s="45"/>
+      <c r="AQ23" s="45"/>
+      <c r="AR23" s="45"/>
+      <c r="AS23" s="45"/>
+      <c r="AT23" s="45"/>
+      <c r="AU23" s="45"/>
+      <c r="AV23" s="45"/>
+      <c r="AW23" s="45"/>
+      <c r="AX23" s="45"/>
+      <c r="AY23" s="45"/>
+      <c r="AZ23" s="45"/>
+      <c r="BA23" s="45"/>
+      <c r="BB23" s="45"/>
+      <c r="BC23" s="45"/>
+      <c r="BD23" s="45"/>
+      <c r="BE23" s="45"/>
+      <c r="BF23" s="45"/>
+      <c r="BG23" s="45"/>
+      <c r="BH23" s="45"/>
+      <c r="BI23" s="45"/>
+      <c r="BJ23" s="45"/>
+      <c r="BK23" s="45"/>
     </row>
     <row r="24" spans="2:63" ht="13.8" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="31"/>
-      <c r="C24" s="31"/>
-      <c r="D24" s="31"/>
-      <c r="E24" s="31"/>
-      <c r="F24" s="31"/>
-      <c r="G24" s="31"/>
-      <c r="H24" s="31"/>
-      <c r="I24" s="31"/>
-      <c r="J24" s="31"/>
-      <c r="K24" s="31"/>
-      <c r="L24" s="31"/>
-      <c r="M24" s="31"/>
-      <c r="N24" s="31"/>
-      <c r="O24" s="31"/>
-      <c r="P24" s="31"/>
-      <c r="Q24" s="31"/>
-      <c r="R24" s="31"/>
-      <c r="S24" s="31"/>
-      <c r="T24" s="31"/>
-      <c r="U24" s="31"/>
-      <c r="V24" s="31"/>
-      <c r="W24" s="31"/>
-      <c r="X24" s="31"/>
-      <c r="Y24" s="31"/>
-      <c r="Z24" s="31"/>
-      <c r="AA24" s="31"/>
-      <c r="AB24" s="31"/>
-      <c r="AC24" s="31"/>
-      <c r="AD24" s="31"/>
-      <c r="AE24" s="31"/>
-      <c r="AF24" s="31"/>
-      <c r="AG24" s="31"/>
-      <c r="AH24" s="31"/>
-      <c r="AI24" s="31"/>
-      <c r="AJ24" s="31"/>
-      <c r="AK24" s="31"/>
-      <c r="AL24" s="31"/>
-      <c r="AM24" s="31"/>
-      <c r="AN24" s="31"/>
-      <c r="AO24" s="31"/>
-      <c r="AP24" s="31"/>
-      <c r="AQ24" s="31"/>
-      <c r="AR24" s="31"/>
-      <c r="AS24" s="31"/>
-      <c r="AT24" s="31"/>
-      <c r="AU24" s="31"/>
-      <c r="AV24" s="31"/>
-      <c r="AW24" s="31"/>
-      <c r="AX24" s="31"/>
-      <c r="AY24" s="31"/>
-      <c r="AZ24" s="31"/>
-      <c r="BA24" s="31"/>
-      <c r="BB24" s="31"/>
-      <c r="BC24" s="31"/>
-      <c r="BD24" s="31"/>
-      <c r="BE24" s="31"/>
-      <c r="BF24" s="31"/>
-      <c r="BG24" s="31"/>
-      <c r="BH24" s="31"/>
-      <c r="BI24" s="31"/>
-      <c r="BJ24" s="31"/>
+      <c r="B24" s="4"/>
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
+      <c r="E24" s="4"/>
+      <c r="F24" s="4"/>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4"/>
+      <c r="I24" s="4"/>
+      <c r="J24" s="4"/>
+      <c r="K24" s="4"/>
+      <c r="L24" s="4"/>
+      <c r="M24" s="4"/>
+      <c r="N24" s="4"/>
+      <c r="O24" s="4"/>
+      <c r="P24" s="4"/>
+      <c r="Q24" s="4"/>
+      <c r="R24" s="4"/>
+      <c r="S24" s="4"/>
+      <c r="T24" s="4"/>
+      <c r="U24" s="4"/>
+      <c r="V24" s="4"/>
+      <c r="W24" s="4"/>
+      <c r="X24" s="4"/>
+      <c r="Y24" s="4"/>
+      <c r="Z24" s="4"/>
+      <c r="AA24" s="4"/>
+      <c r="AB24" s="4"/>
+      <c r="AC24" s="4"/>
+      <c r="AD24" s="4"/>
+      <c r="AE24" s="4"/>
+      <c r="AF24" s="4"/>
+      <c r="AG24" s="4"/>
+      <c r="AH24" s="4"/>
+      <c r="AI24" s="4"/>
+      <c r="AJ24" s="4"/>
+      <c r="AK24" s="4"/>
+      <c r="AL24" s="4"/>
+      <c r="AM24" s="4"/>
+      <c r="AN24" s="4"/>
+      <c r="AO24" s="4"/>
+      <c r="AP24" s="4"/>
+      <c r="AQ24" s="4"/>
+      <c r="AR24" s="4"/>
+      <c r="AS24" s="4"/>
+      <c r="AT24" s="4"/>
+      <c r="AU24" s="4"/>
+      <c r="AV24" s="4"/>
+      <c r="AW24" s="4"/>
+      <c r="AX24" s="4"/>
+      <c r="AY24" s="4"/>
+      <c r="AZ24" s="4"/>
+      <c r="BA24" s="4"/>
+      <c r="BB24" s="4"/>
+      <c r="BC24" s="4"/>
+      <c r="BD24" s="4"/>
+      <c r="BE24" s="4"/>
+      <c r="BF24" s="4"/>
+      <c r="BG24" s="4"/>
+      <c r="BH24" s="4"/>
+      <c r="BI24" s="4"/>
+      <c r="BJ24" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="57">
+    <mergeCell ref="C15:BJ15"/>
+    <mergeCell ref="B4:B21"/>
     <mergeCell ref="B2:BJ2"/>
     <mergeCell ref="O21:Q21"/>
     <mergeCell ref="C21:N21"/>
     <mergeCell ref="AA10:AH10"/>
     <mergeCell ref="BA7:BJ7"/>
     <mergeCell ref="AW10:BC10"/>
+    <mergeCell ref="C10:J10"/>
+    <mergeCell ref="AI10:AO10"/>
+    <mergeCell ref="AE5:AH5"/>
+    <mergeCell ref="AA16:AH16"/>
+    <mergeCell ref="AE17:AH17"/>
+    <mergeCell ref="S16:Z16"/>
+    <mergeCell ref="AD21:AF21"/>
+    <mergeCell ref="R21:AC21"/>
+    <mergeCell ref="C16:J16"/>
+    <mergeCell ref="W7:AF7"/>
+    <mergeCell ref="K10:R10"/>
+    <mergeCell ref="BC13:BJ13"/>
     <mergeCell ref="B23:BK23"/>
     <mergeCell ref="AW16:BC16"/>
     <mergeCell ref="AV21:BG21"/>
     <mergeCell ref="C13:J13"/>
     <mergeCell ref="C18:BJ18"/>
-    <mergeCell ref="C10:J10"/>
     <mergeCell ref="AG21:AR21"/>
     <mergeCell ref="K16:R16"/>
     <mergeCell ref="AF13:AG13"/>
@@ -2125,25 +3190,17 @@
     <mergeCell ref="BD16:BJ16"/>
     <mergeCell ref="AH13:AL13"/>
     <mergeCell ref="AO13:AS13"/>
-    <mergeCell ref="AT13:AU13"/>
-    <mergeCell ref="AI10:AO10"/>
-    <mergeCell ref="AA13:AE13"/>
-    <mergeCell ref="C15:BJ15"/>
-    <mergeCell ref="B4:B21"/>
-    <mergeCell ref="AE5:AH5"/>
-    <mergeCell ref="AA16:AH16"/>
-    <mergeCell ref="AE17:AH17"/>
-    <mergeCell ref="S16:Z16"/>
-    <mergeCell ref="AD21:AF21"/>
-    <mergeCell ref="R21:AC21"/>
-    <mergeCell ref="C7:L7"/>
-    <mergeCell ref="M7:V7"/>
+    <mergeCell ref="BA13:BB13"/>
+    <mergeCell ref="AP10:AV10"/>
     <mergeCell ref="T13:X13"/>
     <mergeCell ref="C9:BJ9"/>
     <mergeCell ref="C6:BJ6"/>
-    <mergeCell ref="C16:J16"/>
-    <mergeCell ref="W7:AF7"/>
-    <mergeCell ref="K10:R10"/>
+    <mergeCell ref="AT13:AU13"/>
+    <mergeCell ref="AA13:AE13"/>
+    <mergeCell ref="C7:L7"/>
+    <mergeCell ref="M7:V7"/>
+    <mergeCell ref="C4:BJ4"/>
+    <mergeCell ref="AM13:AN13"/>
     <mergeCell ref="BH21:BJ21"/>
     <mergeCell ref="K13:L13"/>
     <mergeCell ref="S10:Z10"/>
@@ -2158,11 +3215,6 @@
     <mergeCell ref="AV13:AZ13"/>
     <mergeCell ref="AP16:AV16"/>
     <mergeCell ref="R13:S13"/>
-    <mergeCell ref="BA13:BB13"/>
-    <mergeCell ref="AP10:AV10"/>
-    <mergeCell ref="BC13:BJ13"/>
-    <mergeCell ref="C4:BJ4"/>
-    <mergeCell ref="AM13:AN13"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2171,7 +3223,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{799E8F67-B048-43E1-9D6F-7B18FE32C2F9}">
   <dimension ref="B2:E14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -2184,164 +3236,164 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:5" ht="50.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="56" t="s">
         <v>59</v>
       </c>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
+      <c r="C2" s="56"/>
+      <c r="D2" s="56"/>
+      <c r="E2" s="56"/>
     </row>
     <row r="4" spans="2:5" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="B4" s="29" t="s">
+      <c r="B4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="29" t="s">
+      <c r="C4" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="29" t="s">
+      <c r="D4" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E4" s="29" t="s">
+      <c r="E4" s="3" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="5" spans="2:5" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="B5" s="32" t="s">
+      <c r="B5" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="27" t="s">
+      <c r="C5" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="27" t="s">
+      <c r="D5" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="E5" s="27" t="s">
+      <c r="E5" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="6" spans="2:5" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="B6" s="32" t="s">
+      <c r="B6" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="27" t="s">
+      <c r="C6" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D6" s="27" t="s">
+      <c r="D6" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="27" t="s">
+      <c r="E6" s="2" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="7" spans="2:5" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="B7" s="32" t="s">
+      <c r="B7" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C7" s="27" t="s">
+      <c r="C7" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D7" s="27" t="s">
+      <c r="D7" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="E7" s="27" t="s">
+      <c r="E7" s="2" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="8" spans="2:5" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="B8" s="32" t="s">
+      <c r="B8" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C8" s="27" t="s">
+      <c r="C8" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D8" s="27" t="s">
+      <c r="D8" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="E8" s="27" t="s">
+      <c r="E8" s="2" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="9" spans="2:5" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="B9" s="32" t="s">
+      <c r="B9" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C9" s="27" t="s">
+      <c r="C9" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D9" s="27" t="s">
+      <c r="D9" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="E9" s="27" t="s">
+      <c r="E9" s="2" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="10" spans="2:5" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="B10" s="32" t="s">
+      <c r="B10" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C10" s="27" t="s">
+      <c r="C10" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D10" s="27" t="s">
+      <c r="D10" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="E10" s="27" t="s">
+      <c r="E10" s="2" t="s">
         <v>45</v>
       </c>
     </row>
     <row r="11" spans="2:5" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="B11" s="32" t="s">
+      <c r="B11" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="C11" s="27" t="s">
+      <c r="C11" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D11" s="27" t="s">
+      <c r="D11" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="E11" s="27" t="s">
+      <c r="E11" s="2" t="s">
         <v>48</v>
       </c>
     </row>
     <row r="12" spans="2:5" ht="82.8" x14ac:dyDescent="0.3">
-      <c r="B12" s="32" t="s">
+      <c r="B12" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="C12" s="27" t="s">
+      <c r="C12" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D12" s="27" t="s">
+      <c r="D12" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="E12" s="27" t="s">
+      <c r="E12" s="2" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="13" spans="2:5" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="B13" s="32" t="s">
+      <c r="B13" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="C13" s="27" t="s">
+      <c r="C13" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D13" s="27" t="s">
+      <c r="D13" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E13" s="27" t="s">
+      <c r="E13" s="2" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="14" spans="2:5" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="B14" s="32" t="s">
+      <c r="B14" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C14" s="27" t="s">
+      <c r="C14" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="D14" s="27" t="s">
+      <c r="D14" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E14" s="27" t="s">
+      <c r="E14" s="2" t="s">
         <v>58</v>
       </c>
     </row>
@@ -2354,7 +3406,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E0091C4-CA2C-4A52-9CFD-D039247B100F}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
